--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260930.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260930.xlsx
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>2,335,000</t>
+          <t>11,279,100</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>27,911,000</t>
+          <t>2,335,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>11,279,100</t>
+          <t>27,911,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>16,031,073</t>
+          <t>1,973,678</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,973,678</t>
+          <t>16,031,073</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>2,937,000</t>
+          <t>3,881,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,881,000</t>
+          <t>2,937,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
